--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1325,6 +1325,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -7230,7 +7234,7 @@
         <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>415</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7245,7 +7249,7 @@
         <v>405</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7253,10 +7257,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7282,10 +7286,10 @@
         <v>411</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7336,7 +7340,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7348,7 +7352,7 @@
         <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>415</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7363,7 +7367,7 @@
         <v>405</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7371,10 +7375,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7400,10 +7404,10 @@
         <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7433,10 +7437,10 @@
         <v>329</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7454,7 +7458,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7481,7 +7485,7 @@
         <v>405</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7489,10 +7493,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7518,16 +7522,16 @@
         <v>235</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7555,10 +7559,10 @@
         <v>240</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7576,7 +7580,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7597,10 +7601,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>344</v>
@@ -7611,10 +7615,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7640,16 +7644,16 @@
         <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7677,10 +7681,10 @@
         <v>358</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7698,7 +7702,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7719,10 +7723,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>344</v>
@@ -7733,10 +7737,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7759,17 +7763,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7818,7 +7822,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7845,7 +7849,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7853,10 +7857,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7879,13 +7883,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7936,7 +7940,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7963,7 +7967,7 @@
         <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7971,10 +7975,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7997,16 +8001,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8056,7 +8060,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8080,7 +8084,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>201</v>
@@ -8091,10 +8095,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8117,16 +8121,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8176,7 +8180,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8200,10 +8204,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8211,10 +8215,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8240,16 +8244,16 @@
         <v>179</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8298,7 +8302,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8322,10 +8326,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8333,10 +8337,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8451,10 +8455,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8571,10 +8575,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8693,10 +8697,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8722,13 +8726,13 @@
         <v>235</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>250</v>
@@ -8759,10 +8763,10 @@
         <v>358</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8780,7 +8784,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>94</v>
@@ -8801,7 +8805,7 @@
         <v>254</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>256</v>
@@ -8815,10 +8819,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8841,16 +8845,16 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>316</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>318</v>
@@ -8902,7 +8906,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8923,7 +8927,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>321</v>
@@ -8937,10 +8941,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8966,13 +8970,13 @@
         <v>235</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>328</v>
@@ -9024,7 +9028,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9059,10 +9063,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9146,7 +9150,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9181,10 +9185,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9210,10 +9214,10 @@
         <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>402</v>
@@ -9268,7 +9272,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
